--- a/docs/設計書/04_テーブル定義書.xlsx
+++ b/docs/設計書/04_テーブル定義書.xlsx
@@ -8,18 +8,19 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="テーブル一覧" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ER概要" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="m_product" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="m_supplier" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="m_operator" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="t_stock" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="t_order" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="t_order_detail" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="t_delivery" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="t_delivery_detail" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="t_sales" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="t_stocktaking" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="質問回答による変更点" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版1.1 変更点" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ER概要" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="m_product" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="m_supplier" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="m_operator" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="t_stock" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="t_order" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="t_order_detail" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="t_delivery" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="t_delivery_detail" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="t_sales" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="t_stocktaking" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="質問回答による変更点" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -61,7 +62,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -81,6 +82,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -110,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -134,6 +140,11 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -499,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -520,7 +531,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>お土産屋さん用 発注管理システム　テーブル定義書　版1.0（質問書回答反映済み）　2026/09/28</t>
+          <t>お土産屋さん用 発注管理システム　テーブル定義書　版1.1（0930 修正反映）　2026/09/30</t>
         </is>
       </c>
     </row>
@@ -906,6 +917,18 @@
       <c r="B18" s="7" t="inlineStr">
         <is>
           <t>全テーブル共通カラム（命名規則 2.4 参照）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>青色</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>版1.1（2026/09/30 修正）で説明を追加・変更したセル（カラムの追加・削除はなし）</t>
         </is>
       </c>
     </row>
@@ -916,6 +939,478 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>t_delivery　（納品伝票（ヘッダ））</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>お土産屋さん用 発注管理システム　テーブル定義書　版1.1（0930 修正反映）　2026/09/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>納品1回＝1伝票。卸業者ごとに1枚。確定すると在庫が増える。確定後は変更不可、訂正はマイナス数量の新規伝票。返品も is_return=1 のマイナス伝票としてここに持ち、納品確定で在庫が減る（質問No.4）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>論理名</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>物理名</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>NULL制約</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>キー</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>初期値</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>納品伝票No</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>delivery_no</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>AUTO_INCREMENT</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>納品日</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>delivery_date</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>卸業者コード</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>supplier_code</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>→ m_supplier</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>返品区分</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>is_return</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>TINYINT(1)</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="n"/>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>0=納品 1=返品（質問No.4）。未納品数の計算では 1 を除外する</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>確定フラグ</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>is_confirmed</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>TINYINT(1)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>0=未確定 1=確定済。1の行は以後 UPDATE/DELETE 禁止。0の伝票（返品伝票を含む）は納品確定画面から明細ごと削除できる</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>確定日時</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>confirmed_at</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>確定した日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>確定者</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>confirmed_by</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>確定した操作者コード</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr"/>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>作成者</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>created_by</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr"/>
+      <c r="G14" s="10" t="inlineStr"/>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>作成した操作者コード</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>更新日時</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr"/>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP ON UPDATE</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>更新日時</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>更新者</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>updated_by</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr"/>
+      <c r="G16" s="10" t="inlineStr"/>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>更新した操作者コード</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -944,7 +1439,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>お土産屋さん用 発注管理システム　テーブル定義書　版1.0（質問書回答反映済み）　2026/09/28</t>
+          <t>お土産屋さん用 発注管理システム　テーブル定義書　版1.1（0930 修正反映）　2026/09/30</t>
         </is>
       </c>
     </row>
@@ -1204,9 +1699,9 @@
       </c>
       <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>マイナス可（訂正・返品）</t>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>マイナス可（訂正・返品）。マイナス訂正は納品済数まで（全量納品済みの明細も訂正できる）。残数を超える納品は警告のうえ承知チェックで登録可</t>
         </is>
       </c>
     </row>
@@ -1300,9 +1795,9 @@
       </c>
       <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>返品伝票では返品理由を入れる（質問No.4）</t>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>返品伝票では返品理由を入れる（必須。質問No.4）</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1946,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1480,7 +1975,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>お土産屋さん用 発注管理システム　テーブル定義書　版1.0（質問書回答反映済み）　2026/09/28</t>
+          <t>お土産屋さん用 発注管理システム　テーブル定義書　版1.1（0930 修正反映）　2026/09/30</t>
         </is>
       </c>
     </row>
@@ -1959,7 +2454,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1988,7 +2483,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>お土産屋さん用 発注管理システム　テーブル定義書　版1.0（質問書回答反映済み）　2026/09/28</t>
+          <t>お土産屋さん用 発注管理システム　テーブル定義書　版1.1（0930 修正反映）　2026/09/30</t>
         </is>
       </c>
     </row>
@@ -2415,7 +2910,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2440,7 +2935,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>お土産屋さん用 発注管理システム　テーブル定義書　版1.0（質問書回答反映済み）　2026/09/28</t>
+          <t>お土産屋さん用 発注管理システム　テーブル定義書　版1.1（0930 修正反映）　2026/09/30</t>
         </is>
       </c>
     </row>
@@ -2676,9 +3171,9 @@
           <t>バックアップ・保存期間</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>運用対応 → テーブル変更なし（運用手順書に記載）</t>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>運用対応 → テーブル変更なし。docs/運用手順書.md に記載（週次フル＋日次差分バックアップ：tools/backup_db.sh、5年保持の削除：tools/purge_old_data.php）</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -2754,6 +3249,297 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>版1.1 の変更点（2026/09/30 仕様差異チェック後の修正を反映）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>お土産屋さん用 発注管理システム　テーブル定義書　版1.1（0930 修正反映）　2026/09/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>反映内容</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>影響テーブル</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>確定済み伝票の例外</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>t_order.mailed_at は確定後も更新してよい（発注書メールの送信・再送）。開発モードでは更新しない</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>t_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>未確定伝票の削除</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>未確定（is_confirmed=0）の発注伝票・納品伝票（返品含む）は明細ごと物理削除できる。確定済みは従来どおり不可</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>t_order, t_order_detail, t_delivery, t_delivery_detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>取消行の単価・卸業者</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>マイナス（取消）行は取消元の発注明細の契約単価・卸業者をコピー。取消できる数は未確定の取消も差し引いて判定し、確定時に再チェック</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>t_order, t_order_detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>未納品数の計算</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>SC-20 は未確定の納品も差し引く（二重入力防止）。SC-22 は確定済みで計算し未確定分は別列表示</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>t_order_detail, t_delivery_detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>納品のマイナス訂正・超過</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>全量納品済みの明細も納品済数まで訂正できる。残数超過は警告＋承知チェックで登録可</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>t_delivery_detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>操作者の権限</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>承認不可の操作者は自分の操作者名・メールのみ変更可。権限変更・削除はログイン中にも即時反映</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>m_operator</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>入力チェック</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>商品・卸業者コードは英数字のみ、JAN は13桁＋チェックデジット、商品名カナは全角カタカナ</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>m_product, m_supplier</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>運用（質問No.11）</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>バックアップ・5年保持の削除手順を docs/運用手順書.md と tools/ に用意</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>今後の検討（未反映）</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>要件「いつ納品されるか一目でわかるように」→ 納品予定日の列（t_order または t_order_detail）の追加を検討。「在庫不足」→ 発注点（m_product）の追加を検討。どちらも顧客確認後に決める</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>t_order / t_order_detail, m_product</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2780,7 +3566,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>お土産屋さん用 発注管理システム　テーブル定義書　版1.0（質問書回答反映済み）　2026/09/28</t>
+          <t>お土産屋さん用 発注管理システム　テーブル定義書　版1.1（0930 修正反映）　2026/09/30</t>
         </is>
       </c>
     </row>
@@ -3222,7 +4008,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3251,7 +4037,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>お土産屋さん用 発注管理システム　テーブル定義書　版1.0（質問書回答反映済み）　2026/09/28</t>
+          <t>お土産屋さん用 発注管理システム　テーブル定義書　版1.1（0930 修正反映）　2026/09/30</t>
         </is>
       </c>
     </row>
@@ -3335,9 +4121,9 @@
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>英数字。画面で入力</t>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>英数字のみ（記号不可）。画面で入力</t>
         </is>
       </c>
     </row>
@@ -3395,9 +4181,9 @@
       </c>
       <c r="F8" s="11" t="n"/>
       <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="inlineStr">
-        <is>
-          <t>全角カタカナ。一覧はこの昇順で並べる（質問No.1）</t>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>全角カタカナ（ァ〜ヶ・ヴ・ー・中黒・全角スペース）。一覧はこの昇順で並べる（質問No.1）</t>
         </is>
       </c>
     </row>
@@ -3531,9 +4317,9 @@
       </c>
       <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>13桁</t>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>13桁の数字。チェックデジット（13桁目）を検証する</t>
         </is>
       </c>
     </row>
@@ -3699,9 +4485,9 @@
       </c>
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>img/product/ 配下のファイル名。DBに画像は入れない</t>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>img/product/ 配下のファイル名（商品コード.拡張子）。DBに画像は入れない。差し替え・削除時は古いファイルも消す。本番は Volume に保存</t>
         </is>
       </c>
     </row>
@@ -3982,7 +4768,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4011,7 +4797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>お土産屋さん用 発注管理システム　テーブル定義書　版1.0（質問書回答反映済み）　2026/09/28</t>
+          <t>お土産屋さん用 発注管理システム　テーブル定義書　版1.1（0930 修正反映）　2026/09/30</t>
         </is>
       </c>
     </row>
@@ -4095,9 +4881,9 @@
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>英数字。画面で入力</t>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>英数字のみ（記号不可）。画面で入力</t>
         </is>
       </c>
     </row>
@@ -4426,7 +5212,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4455,7 +5241,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>お土産屋さん用 発注管理システム　テーブル定義書　版1.0（質問書回答反映済み）　2026/09/28</t>
+          <t>お土産屋さん用 発注管理システム　テーブル定義書　版1.1（0930 修正反映）　2026/09/30</t>
         </is>
       </c>
     </row>
@@ -4667,9 +5453,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
-        <is>
-          <t>1=発注確定できる。権限はこの1つのみ（質問No.5）。操作者のパスワード設定もこの権限者が行う</t>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>1=発注確定できる。権限はこの1つのみ（質問No.5）。操作者の新規登録・他人の編集・削除・パスワード設定もこの権限者が行う。承認不可(0)の操作者は自分の操作者名・メールのみ変更できる。変更はログイン中の操作者にも次の操作から反映</t>
         </is>
       </c>
     </row>
@@ -4854,7 +5640,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4883,7 +5669,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>お土産屋さん用 発注管理システム　テーブル定義書　版1.0（質問書回答反映済み）　2026/09/28</t>
+          <t>お土産屋さん用 発注管理システム　テーブル定義書　版1.1（0930 修正反映）　2026/09/30</t>
         </is>
       </c>
     </row>
@@ -4894,6 +5680,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -5153,7 +5940,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5182,7 +5969,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>お土産屋さん用 発注管理システム　テーブル定義書　版1.0（質問書回答反映済み）　2026/09/28</t>
+          <t>お土産屋さん用 発注管理システム　テーブル定義書　版1.1（0930 修正反映）　2026/09/30</t>
         </is>
       </c>
     </row>
@@ -5366,9 +6153,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>0=未確定 1=確定済。1の行は以後 UPDATE/DELETE 禁止</t>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>0=未確定 1=確定済。1の行は以後 UPDATE/DELETE 禁止（例外：mailed_at の更新のみ可）。0の伝票は発注確定画面から明細ごと削除できる</t>
         </is>
       </c>
     </row>
@@ -5474,9 +6261,9 @@
           <t>NULL</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>発注書PDFを卸業者へメール送信した日時。NULL=未送信（質問No.6）</t>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>発注書PDFを卸業者へメール送信した日時。NULL=未送信（質問No.6）。開発モード（MAIL_DRIVER=log）では実際に送らないため更新しない</t>
         </is>
       </c>
     </row>
@@ -5542,9 +6329,9 @@
       </c>
       <c r="F14" s="10" t="inlineStr"/>
       <c r="G14" s="10" t="inlineStr"/>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>作成した操作者コード</t>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>作成（起票）した操作者コード。発注確定・発注書・発注明細表に起票者として表示</t>
         </is>
       </c>
     </row>
@@ -5625,7 +6412,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5654,7 +6441,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>お土産屋さん用 発注管理システム　テーブル定義書　版1.0（質問書回答反映済み）　2026/09/28</t>
+          <t>お土産屋さん用 発注管理システム　テーブル定義書　版1.1（0930 修正反映）　2026/09/30</t>
         </is>
       </c>
     </row>
@@ -5874,9 +6661,9 @@
       </c>
       <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>発注時点の m_product.contract_price をコピー</t>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>発注時点の m_product.contract_price をコピー。マイナス（取消）行は取消元の発注明細の単価をコピー（卸業者も取消元の伝票と同じ）</t>
         </is>
       </c>
     </row>
@@ -5978,9 +6765,9 @@
           <t>NULL</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
-        <is>
-          <t>マイナス行のみ設定。取り消す元の発注明細（質問No.3）</t>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>マイナス行のみ設定。取り消す元の発注明細（質問No.3）。取消できる数＝元明細の未納品数 − 未確定の取消数。発注確定時にも再チェック</t>
         </is>
       </c>
     </row>
@@ -6162,481 +6949,9 @@
     </row>
     <row r="19"/>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>※ 未納品数 = order_qty ＋ SUM(取消明細の order_qty：ref_order_no, ref_line_no が一致) − SUM(t_delivery_detail.delivery_qty：同じ order_no, line_no、かつ is_return=0 の納品伝票)。取消明細（マイナス行）自体は未納品一覧に出さない。列としては持たない（不整合防止）</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A3:H3"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>t_delivery　（納品伝票（ヘッダ））</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>お土産屋さん用 発注管理システム　テーブル定義書　版1.0（質問書回答反映済み）　2026/09/28</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>納品1回＝1伝票。卸業者ごとに1枚。確定すると在庫が増える。確定後は変更不可、訂正はマイナス数量の新規伝票。返品も is_return=1 のマイナス伝票としてここに持ち、納品確定で在庫が減る（質問No.4）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>論理名</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>物理名</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>NULL制約</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>キー</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>初期値</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>納品伝票No</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>delivery_no</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>AUTO_INCREMENT</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>納品日</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>delivery_date</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>卸業者コード</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>supplier_code</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>VARCHAR(10)</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>→ m_supplier</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>返品区分</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>is_return</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>TINYINT(1)</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" s="11" t="inlineStr">
-        <is>
-          <t>0=納品 1=返品（質問No.4）。未納品数の計算では 1 を除外する</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>確定フラグ</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>is_confirmed</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>TINYINT(1)</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>0=未確定 1=確定済。1の行は以後 UPDATE/DELETE 禁止</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>確定日時</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>confirmed_at</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>DATETIME</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>確定した日時</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>確定者</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>confirmed_by</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>VARCHAR(10)</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>確定した操作者コード</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>作成日時</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>DATETIME</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr"/>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>作成日時</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>作成者</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>created_by</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>VARCHAR(10)</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr"/>
-      <c r="G14" s="10" t="inlineStr"/>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>作成した操作者コード</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>更新日時</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>DATETIME</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr"/>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP ON UPDATE</t>
-        </is>
-      </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>更新日時</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>更新者</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>updated_by</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>VARCHAR(10)</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr"/>
-      <c r="G16" s="10" t="inlineStr"/>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>更新した操作者コード</t>
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>※ 未納品数 = order_qty ＋ SUM(確定済み取消明細の order_qty：ref_order_no, ref_line_no が一致) − SUM(t_delivery_detail.delivery_qty：同じ order_no, line_no、かつ is_return=0 の納品伝票)。納品入力（SC-20）は二重入力防止のため未確定の納品も差し引く。未納品一覧表（SC-22）は確定済みの納品で計算し、未確定分は別列に出す。取消明細（マイナス行）自体は未納品一覧に出さない。列としては持たない（不整合防止）</t>
         </is>
       </c>
     </row>
